--- a/data/trans_orig/P36B06_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P36B06_R-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consume fruta fresca (excluyendo zumos) al menos 3 veces por semana en 2007</t>
+          <t>Población que consume fruta fresca (excluyendo zumos) al menos 3 veces por semana en 2007 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>539425</t>
+          <t>538299</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>579623</t>
+          <t>579121</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>571807</t>
+          <t>573425</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>608217</t>
+          <t>608145</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>83,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1123718</t>
+          <t>1122685</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1175397</t>
+          <t>1177736</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>81,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>85,26%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>113441</t>
+          <t>113943</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>153639</t>
+          <t>154765</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>80134</t>
+          <t>80206</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>116544</t>
+          <t>114926</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>206018</t>
+          <t>203679</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>257697</t>
+          <t>258730</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,73%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>675023</t>
+          <t>673434</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>734811</t>
+          <t>731530</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>70,26%</t>
+          <t>70,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>733580</t>
+          <t>732289</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>783382</t>
+          <t>785117</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>75,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>81,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1426008</t>
+          <t>1424149</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1500089</t>
+          <t>1501618</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>73,96%</t>
+          <t>73,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>77,8%</t>
+          <t>77,88%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>225947</t>
+          <t>229228</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>285735</t>
+          <t>287324</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>183951</t>
+          <t>182216</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>233753</t>
+          <t>235044</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>428002</t>
+          <t>426473</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>502083</t>
+          <t>503942</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>26,14%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>503480</t>
+          <t>506417</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>547731</t>
+          <t>548803</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>74,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>80,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>545344</t>
+          <t>547141</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>584168</t>
+          <t>584919</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1061468</t>
+          <t>1062352</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1121705</t>
+          <t>1121234</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>82,3%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>130778</t>
+          <t>129706</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>175029</t>
+          <t>172092</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>99673</t>
+          <t>98922</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>138497</t>
+          <t>136700</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>240645</t>
+          <t>241116</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>300882</t>
+          <t>299998</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,02%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>675910</t>
+          <t>675605</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>726604</t>
+          <t>728856</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>71,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>77,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>813062</t>
+          <t>813688</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>863955</t>
+          <t>863478</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1507757</t>
+          <t>1504014</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1579903</t>
+          <t>1576334</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>79,65%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>214736</t>
+          <t>212484</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>265430</t>
+          <t>265735</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>173681</t>
+          <t>174158</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>224574</t>
+          <t>223948</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>399074</t>
+          <t>402643</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>471220</t>
+          <t>474963</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>24,0%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2449382</t>
+          <t>2451498</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2544630</t>
+          <t>2550722</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2709677</t>
+          <t>2713392</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2799375</t>
+          <t>2798214</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5177785</t>
+          <t>5185270</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5322608</t>
+          <t>5322071</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>77,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>80,02%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>729041</t>
+          <t>722949</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>824289</t>
+          <t>822173</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>577787</t>
+          <t>578948</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>667485</t>
+          <t>663770</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1328225</t>
+          <t>1328762</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1473048</t>
+          <t>1465563</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,04%</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consume fruta fresca (excluyendo zumos) al menos 3 veces por semana en 2012</t>
+          <t>Población que consume fruta fresca (excluyendo zumos) al menos 3 veces por semana en 2012 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>590955</t>
+          <t>590611</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>626331</t>
+          <t>626729</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>609543</t>
+          <t>609377</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>640531</t>
+          <t>642379</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1208423</t>
+          <t>1208877</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1258268</t>
+          <t>1259009</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,9%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>77138</t>
+          <t>76740</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>112514</t>
+          <t>112858</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>56519</t>
+          <t>54671</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>87507</t>
+          <t>87673</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>142251</t>
+          <t>141510</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>192096</t>
+          <t>191642</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,68%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>809257</t>
+          <t>809692</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>858914</t>
+          <t>860192</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>79,73%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>879072</t>
+          <t>881243</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>924552</t>
+          <t>925949</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1705847</t>
+          <t>1707148</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1772354</t>
+          <t>1771955</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,6%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>156080</t>
+          <t>154802</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>205737</t>
+          <t>205302</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>106545</t>
+          <t>105148</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>152025</t>
+          <t>149854</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>273737</t>
+          <t>274136</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>340244</t>
+          <t>338943</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,57%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>610679</t>
+          <t>612132</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>652926</t>
+          <t>652374</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>651482</t>
+          <t>649609</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>690761</t>
+          <t>688966</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1270490</t>
+          <t>1273340</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1332371</t>
+          <t>1333280</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>87,11%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>102588</t>
+          <t>103140</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>144835</t>
+          <t>143382</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>84255</t>
+          <t>86050</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>123534</t>
+          <t>125407</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>198159</t>
+          <t>197250</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>260040</t>
+          <t>257190</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,8%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>755391</t>
+          <t>752089</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>803438</t>
+          <t>799113</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>84,77%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>888519</t>
+          <t>892333</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>932763</t>
+          <t>935645</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1657679</t>
+          <t>1658390</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1723772</t>
+          <t>1719131</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,15%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>144301</t>
+          <t>148626</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>192348</t>
+          <t>195650</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>115047</t>
+          <t>112165</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>159291</t>
+          <t>155477</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>271777</t>
+          <t>276418</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>337870</t>
+          <t>337159</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,9%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2812667</t>
+          <t>2801621</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2899943</t>
+          <t>2893006</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3078892</t>
+          <t>3070752</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3154466</t>
+          <t>3152914</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5912374</t>
+          <t>5907117</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6029929</t>
+          <t>6026951</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,44%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>521774</t>
+          <t>528711</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>609050</t>
+          <t>620096</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>396506</t>
+          <t>398058</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>472080</t>
+          <t>480220</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>942760</t>
+          <t>945738</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1060315</t>
+          <t>1065572</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,28%</t>
         </is>
       </c>
     </row>
@@ -4431,7 +4431,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consume fruta fresca (excluyendo zumos) al menos 3 veces por semana en 2016</t>
+          <t>Población que consume fruta fresca (excluyendo zumos) al menos 3 veces por semana en 2016 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4626,12 +4626,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>522960</t>
+          <t>521485</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>565633</t>
+          <t>565009</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>77,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>531941</t>
+          <t>529580</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>570544</t>
+          <t>569503</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>78,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1065908</t>
+          <t>1066529</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1124085</t>
+          <t>1124990</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>79,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>83,54%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>108118</t>
+          <t>108742</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>150791</t>
+          <t>152266</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>102295</t>
+          <t>103336</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>140898</t>
+          <t>143259</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>222505</t>
+          <t>221600</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>280682</t>
+          <t>280061</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,8%</t>
         </is>
       </c>
     </row>
@@ -4969,12 +4969,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>782001</t>
+          <t>781378</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>832985</t>
+          <t>835300</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>76,7%</t>
+          <t>76,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>809177</t>
+          <t>808538</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>865679</t>
+          <t>863669</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>77,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1612051</t>
+          <t>1612181</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1682230</t>
+          <t>1684969</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>78,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>81,84%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>186639</t>
+          <t>184324</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>237623</t>
+          <t>238246</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>173512</t>
+          <t>175522</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>230014</t>
+          <t>230653</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>376586</t>
+          <t>373847</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>446765</t>
+          <t>446635</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,69%</t>
         </is>
       </c>
     </row>
@@ -5312,12 +5312,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>566592</t>
+          <t>564751</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>615969</t>
+          <t>611773</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>74,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>80,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>641909</t>
+          <t>640933</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>682425</t>
+          <t>682453</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1223137</t>
+          <t>1220640</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1284661</t>
+          <t>1285757</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>83,3%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>142597</t>
+          <t>146793</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>191974</t>
+          <t>193815</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>102586</t>
+          <t>102558</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>143102</t>
+          <t>144078</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>258916</t>
+          <t>257820</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>320440</t>
+          <t>322937</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,92%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>739327</t>
+          <t>742230</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>788132</t>
+          <t>790229</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>79,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>876389</t>
+          <t>875461</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>920968</t>
+          <t>918953</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1633459</t>
+          <t>1633140</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1697508</t>
+          <t>1696960</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>85,82%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>147478</t>
+          <t>145381</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>196283</t>
+          <t>193380</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>120703</t>
+          <t>122718</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>165282</t>
+          <t>166210</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>279773</t>
+          <t>280321</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>343822</t>
+          <t>344141</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,4%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2660576</t>
+          <t>2663191</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2752130</t>
+          <t>2759808</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2905980</t>
+          <t>2906414</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2993329</t>
+          <t>2999309</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5590496</t>
+          <t>5597182</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5724540</t>
+          <t>5726172</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>82,67%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>635420</t>
+          <t>627742</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>726974</t>
+          <t>724359</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>545383</t>
+          <t>539403</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>632732</t>
+          <t>632298</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1201723</t>
+          <t>1200091</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1335767</t>
+          <t>1329081</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,19%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36B06_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P36B06_R-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>538299</t>
+          <t>539892</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>579121</t>
+          <t>580709</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>77,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>573425</t>
+          <t>574290</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>608145</t>
+          <t>607959</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1122685</t>
+          <t>1121440</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1177736</t>
+          <t>1176265</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>85,15%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>113943</t>
+          <t>112355</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>154765</t>
+          <t>153172</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>80206</t>
+          <t>80392</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>114926</t>
+          <t>114061</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>203679</t>
+          <t>205150</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>258730</t>
+          <t>259975</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,82%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>673434</t>
+          <t>676991</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>731530</t>
+          <t>732836</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>732289</t>
+          <t>731512</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>785117</t>
+          <t>784316</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>75,7%</t>
+          <t>75,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1424149</t>
+          <t>1424576</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1501618</t>
+          <t>1504267</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>73,86%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>78,02%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>229228</t>
+          <t>227922</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>287324</t>
+          <t>283767</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>182216</t>
+          <t>183017</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>235044</t>
+          <t>235821</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>426473</t>
+          <t>423824</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>503942</t>
+          <t>503515</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,11%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>506417</t>
+          <t>502485</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>548803</t>
+          <t>547228</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>74,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>80,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>547141</t>
+          <t>545858</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>584919</t>
+          <t>585133</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1062352</t>
+          <t>1065821</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1121234</t>
+          <t>1123840</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>78,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>82,49%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>129706</t>
+          <t>131281</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>172092</t>
+          <t>176024</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>98922</t>
+          <t>98708</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>136700</t>
+          <t>137983</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>241116</t>
+          <t>238510</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>299998</t>
+          <t>296529</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,77%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>675605</t>
+          <t>675444</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>728856</t>
+          <t>727313</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>813688</t>
+          <t>813859</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>863478</t>
+          <t>862247</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>78,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1504014</t>
+          <t>1504257</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1576334</t>
+          <t>1577934</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>79,65%</t>
+          <t>79,73%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>212484</t>
+          <t>214027</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>265735</t>
+          <t>265896</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>174158</t>
+          <t>175389</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>223948</t>
+          <t>223777</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>402643</t>
+          <t>401043</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>474963</t>
+          <t>474720</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,99%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2451498</t>
+          <t>2446669</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2550722</t>
+          <t>2543041</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>77,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2713392</t>
+          <t>2712791</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2798214</t>
+          <t>2798060</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5185270</t>
+          <t>5188156</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5322071</t>
+          <t>5314879</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>78,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>79,91%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>722949</t>
+          <t>730630</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>822173</t>
+          <t>827002</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>578948</t>
+          <t>579102</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>663770</t>
+          <t>664371</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1328762</t>
+          <t>1335954</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1465563</t>
+          <t>1462677</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,99%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>590611</t>
+          <t>589040</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>626729</t>
+          <t>625062</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>609377</t>
+          <t>609162</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>642379</t>
+          <t>641335</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1208877</t>
+          <t>1209808</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1259009</t>
+          <t>1257386</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>89,78%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>76740</t>
+          <t>78407</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>112858</t>
+          <t>114429</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>54671</t>
+          <t>55715</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>87673</t>
+          <t>87888</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>141510</t>
+          <t>143133</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>191642</t>
+          <t>190711</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,62%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>809692</t>
+          <t>808902</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>860192</t>
+          <t>860084</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>79,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>881243</t>
+          <t>880633</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>925949</t>
+          <t>926718</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1707148</t>
+          <t>1708931</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1771955</t>
+          <t>1775805</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,79%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>154802</t>
+          <t>154910</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>205302</t>
+          <t>206092</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>105148</t>
+          <t>104379</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>149854</t>
+          <t>150464</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>274136</t>
+          <t>270286</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>338943</t>
+          <t>337160</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,48%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>612132</t>
+          <t>608733</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>652374</t>
+          <t>652600</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>80,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>649609</t>
+          <t>648223</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>688966</t>
+          <t>689917</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>83,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1273340</t>
+          <t>1272777</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1333280</t>
+          <t>1331082</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>86,97%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>103140</t>
+          <t>102914</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>143382</t>
+          <t>146781</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>86050</t>
+          <t>85099</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>125407</t>
+          <t>126793</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>197250</t>
+          <t>199448</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>257190</t>
+          <t>257753</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,84%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>752089</t>
+          <t>749956</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>799113</t>
+          <t>800813</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>892333</t>
+          <t>888685</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>935645</t>
+          <t>935123</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1658390</t>
+          <t>1657911</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1719131</t>
+          <t>1723431</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>83,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>86,36%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>148626</t>
+          <t>146926</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>195650</t>
+          <t>197783</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>112165</t>
+          <t>112687</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>155477</t>
+          <t>159125</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>276418</t>
+          <t>272118</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>337159</t>
+          <t>337638</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,92%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2801621</t>
+          <t>2807106</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2893006</t>
+          <t>2901259</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3070752</t>
+          <t>3078052</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3152914</t>
+          <t>3157898</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5907117</t>
+          <t>5907769</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6026951</t>
+          <t>6028474</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>86,46%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>528711</t>
+          <t>520458</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>620096</t>
+          <t>614611</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>398058</t>
+          <t>393074</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>480220</t>
+          <t>472920</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>945738</t>
+          <t>944215</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1065572</t>
+          <t>1064920</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,27%</t>
         </is>
       </c>
     </row>
@@ -4626,12 +4626,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>521485</t>
+          <t>521545</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>565009</t>
+          <t>564352</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>77,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>529580</t>
+          <t>531042</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>569503</t>
+          <t>570174</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>78,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1066529</t>
+          <t>1066738</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1124990</t>
+          <t>1123174</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>83,41%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>108742</t>
+          <t>109399</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>152266</t>
+          <t>152206</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>103336</t>
+          <t>102665</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>143259</t>
+          <t>141797</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>221600</t>
+          <t>223416</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>280061</t>
+          <t>279852</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,78%</t>
         </is>
       </c>
     </row>
@@ -4969,12 +4969,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>781378</t>
+          <t>782365</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>835300</t>
+          <t>832641</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>81,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>808538</t>
+          <t>809350</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>863669</t>
+          <t>862226</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>77,8%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1612181</t>
+          <t>1608753</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1684969</t>
+          <t>1684206</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>81,8%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>184324</t>
+          <t>186983</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>238246</t>
+          <t>237259</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>175522</t>
+          <t>176965</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>230653</t>
+          <t>229841</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>373847</t>
+          <t>374610</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>446635</t>
+          <t>450063</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,86%</t>
         </is>
       </c>
     </row>
@@ -5312,12 +5312,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>564751</t>
+          <t>562234</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>611773</t>
+          <t>612230</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>74,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>640933</t>
+          <t>640265</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>682453</t>
+          <t>682121</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1220640</t>
+          <t>1218106</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1285757</t>
+          <t>1282462</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>78,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,08%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>146793</t>
+          <t>146336</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>193815</t>
+          <t>196332</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>102558</t>
+          <t>102890</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>144078</t>
+          <t>144746</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>257820</t>
+          <t>261115</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>322937</t>
+          <t>325471</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>21,09%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>742230</t>
+          <t>744258</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>790229</t>
+          <t>788593</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>79,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>875461</t>
+          <t>874562</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>918953</t>
+          <t>919323</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1633140</t>
+          <t>1633410</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1696960</t>
+          <t>1698380</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>82,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>85,89%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>145381</t>
+          <t>147017</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>193380</t>
+          <t>191352</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>122718</t>
+          <t>122348</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>166210</t>
+          <t>167109</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>280321</t>
+          <t>278901</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>344141</t>
+          <t>343871</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,39%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2663191</t>
+          <t>2663723</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2759808</t>
+          <t>2756120</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2906414</t>
+          <t>2902820</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2999309</t>
+          <t>2994356</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5597182</t>
+          <t>5591746</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5726172</t>
+          <t>5728970</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,71%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>627742</t>
+          <t>631430</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>724359</t>
+          <t>723827</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>539403</t>
+          <t>544356</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>632298</t>
+          <t>635892</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1200091</t>
+          <t>1197293</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1329081</t>
+          <t>1334517</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,27%</t>
         </is>
       </c>
     </row>
